--- a/data/trans_camb/CAGE_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/CAGE_R-Habitat-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con consumo de riesgo, consumo perudicial o dependencia al alcohol (CAGE)</t>
+          <t>Población con consumo de riesgo, consumo perjudicial o dependencia al alcohol (CAGE)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 1,53</t>
+          <t>-0,42; 1,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 1,49</t>
+          <t>-0,56; 1,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 1,52</t>
+          <t>-0,74; 1,52</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,72</t>
+          <t>0,0; 0,74</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,98</t>
+          <t>0,0; 0,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,12</t>
+          <t>0,0; 3,07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 0,91</t>
+          <t>-0,18; 0,86</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 0,86</t>
+          <t>-0,23; 0,87</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 1,5</t>
+          <t>-0,06; 1,5</t>
         </is>
       </c>
     </row>
@@ -783,17 +783,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-57,34; 762,39</t>
+          <t>-53,85; 689,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-71,99; 738,83</t>
+          <t>-74,47; 548,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-79,18; 654,09</t>
+          <t>-77,53; 778,09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-47,01; 696,53</t>
+          <t>-49,43; 580,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-49,73; 646,78</t>
+          <t>-77,24; 551,18</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-43,09; 1258,58</t>
+          <t>-40,51; 1233,64</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 1,84</t>
+          <t>-0,24; 1,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,68</t>
+          <t>0,4; 2,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,14; 2,96</t>
+          <t>0,16; 3,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 0,19</t>
+          <t>-0,33; 0,19</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 0,57</t>
+          <t>-0,13; 0,64</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,02; 5,66</t>
+          <t>0,97; 5,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 0,86</t>
+          <t>-0,12; 0,92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,48</t>
+          <t>0,25; 1,47</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,92; 3,2</t>
+          <t>0,89; 3,13</t>
         </is>
       </c>
     </row>
@@ -999,17 +999,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-41,93; 460,15</t>
+          <t>-33,78; 521,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>24,37; 692,25</t>
+          <t>14,88; 721,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 712,23</t>
+          <t>2,7; 885,6</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1029,17 +1029,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-31,81; 398,42</t>
+          <t>-27,64; 409,35</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>26,72; 687,44</t>
+          <t>29,2; 664,05</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>113,19; 1266,72</t>
+          <t>117,54; 1282,0</t>
         </is>
       </c>
     </row>
@@ -1109,22 +1109,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 2,91</t>
+          <t>0,21; 3,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 0,99</t>
+          <t>-0,89; 1,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 2,53</t>
+          <t>-0,51; 2,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,67</t>
+          <t>0,0; 0,64</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1134,22 +1134,22 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,04</t>
+          <t>0,0; 3,95</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,46</t>
+          <t>0,13; 1,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 0,5</t>
+          <t>-0,5; 0,52</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 2,45</t>
+          <t>-0,2; 2,29</t>
         </is>
       </c>
     </row>
@@ -1215,17 +1215,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 501,67</t>
+          <t>0,42; 550,16</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-68,07; 214,7</t>
+          <t>-67,97; 251,07</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-51,81; 449,63</t>
+          <t>-54,28; 566,41</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,29; 534,13</t>
+          <t>7,3; 582,7</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-72,19; 218,89</t>
+          <t>-71,8; 213,2</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-32,64; 898,05</t>
+          <t>-31,25; 737,62</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,73; 3,28</t>
+          <t>0,81; 3,42</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 1,44</t>
+          <t>-0,41; 1,48</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,41; 5,53</t>
+          <t>1,43; 5,52</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,37; -0,01</t>
+          <t>-1,32; -0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 1,23</t>
+          <t>-0,57; 1,29</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 1,43</t>
+          <t>-0,71; 1,55</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 1,25</t>
+          <t>-0,02; 1,29</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 1,14</t>
+          <t>-0,19; 1,14</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,77; 3,6</t>
+          <t>0,85; 3,56</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>38,2; 860,61</t>
+          <t>47,69; 812,08</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-41,95; 402,78</t>
+          <t>-40,25; 402,59</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>89,72; 1372,95</t>
+          <t>78,01; 1247,84</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 125,29</t>
+          <t>-100,0; 115,35</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-46,79; 317,85</t>
+          <t>-51,99; 353,45</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-67,49; 369,41</t>
+          <t>-69,02; 332,63</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-18,67; 236,1</t>
+          <t>-6,4; 254,95</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-25,36; 216,66</t>
+          <t>-20,4; 243,47</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>60,3; 622,31</t>
+          <t>72,42; 638,44</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,57; 1,77</t>
+          <t>0,63; 1,79</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,21</t>
+          <t>0,16; 1,24</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,35</t>
+          <t>0,74; 2,45</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 0,08</t>
+          <t>-0,4; 0,07</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 0,51</t>
+          <t>-0,11; 0,49</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,98</t>
+          <t>0,22; 2,03</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,84</t>
+          <t>0,17; 0,78</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,13; 0,75</t>
+          <t>0,11; 0,72</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,77; 2,01</t>
+          <t>0,64; 1,93</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>48,48; 305,79</t>
+          <t>58,31; 310,93</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>13,79; 219,2</t>
+          <t>10,24; 200,54</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>72,37; 400,91</t>
+          <t>75,12; 409,43</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-88,23; 84,49</t>
+          <t>-88,11; 85,72</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-30,01; 337,74</t>
+          <t>-37,4; 312,52</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>63,17; 1178,94</t>
+          <t>50,07; 1035,17</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>28,22; 208,48</t>
+          <t>25,21; 201,8</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>16,83; 188,71</t>
+          <t>17,59; 189,01</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>126,35; 497,5</t>
+          <t>110,68; 455,96</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/CAGE_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/CAGE_R-Habitat-trans_camb.xlsx
@@ -634,37 +634,37 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>0,25</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0,15</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,29</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,76</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0,36</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0,3</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,15</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,29</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,82</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,36</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0,3</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,58</t>
+          <t>0,53</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 1,59</t>
+          <t>-0,46; 1,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 1,35</t>
+          <t>-0,71; 1,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 1,52</t>
+          <t>-0,76; 1,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,74</t>
+          <t>0,0; 0,73</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,99</t>
+          <t>0,0; 0,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,07</t>
+          <t>0,0; 2,71</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 0,86</t>
+          <t>-0,16; 0,93</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 0,87</t>
+          <t>-0,24; 0,92</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 1,5</t>
+          <t>-0,11; 1,35</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>36,92%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>175,43%</t>
+          <t>158,18%</t>
         </is>
       </c>
     </row>
@@ -783,17 +783,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-53,85; 689,47</t>
+          <t>-54,46; 654,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-74,47; 548,75</t>
+          <t>-75,9; 570,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-77,53; 778,09</t>
+          <t>-81,04; 630,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-49,43; 580,84</t>
+          <t>-53,35; 776,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-77,24; 551,18</t>
+          <t>-60,99; 667,5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-40,51; 1233,64</t>
+          <t>-44,45; 1189,73</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,26</t>
+          <t>1,15</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,58</t>
+          <t>2,46</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,78</t>
+          <t>1,67</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 1,83</t>
+          <t>-0,22; 1,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,4; 2,67</t>
+          <t>0,43; 2,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,16; 3,02</t>
+          <t>-0,1; 2,66</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 0,19</t>
+          <t>-0,32; 0,19</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 0,64</t>
+          <t>-0,14; 0,6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,97; 5,56</t>
+          <t>1,0; 5,71</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 0,92</t>
+          <t>-0,21; 0,9</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,47</t>
+          <t>0,23; 1,42</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,89; 3,13</t>
+          <t>0,8; 2,86</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>172,03%</t>
+          <t>157,38%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2422,06%</t>
+          <t>2313,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>425,36%</t>
+          <t>400,99%</t>
         </is>
       </c>
     </row>
@@ -999,17 +999,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-33,78; 521,17</t>
+          <t>-38,53; 384,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,88; 721,17</t>
+          <t>19,3; 638,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,7; 885,6</t>
+          <t>-14,57; 754,53</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1029,17 +1029,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-27,64; 409,35</t>
+          <t>-37,86; 365,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>29,2; 664,05</t>
+          <t>24,78; 589,16</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>117,54; 1282,0</t>
+          <t>112,18; 1247,58</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,7</t>
+          <t>1,73</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,0</t>
+          <t>2,24</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,83</t>
+          <t>2,05</t>
         </is>
       </c>
     </row>
@@ -1109,22 +1109,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,21; 3,0</t>
+          <t>0,11; 2,92</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 1,09</t>
+          <t>-0,94; 1,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 2,84</t>
+          <t>0,02; 4,34</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,64</t>
+          <t>0,0; 0,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1134,22 +1134,22 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,95</t>
+          <t>0,71; 7,97</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,53</t>
+          <t>0,14; 1,48</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 0,52</t>
+          <t>-0,49; 0,55</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 2,29</t>
+          <t>0,87; 4,03</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>71,22%</t>
+          <t>176,29%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>169,49%</t>
+          <t>420,81%</t>
         </is>
       </c>
     </row>
@@ -1215,17 +1215,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,42; 550,16</t>
+          <t>-5,7; 579,87</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-67,97; 251,07</t>
+          <t>-64,98; 284,73</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-54,28; 566,41</t>
+          <t>-13,01; 928,18</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,3; 582,7</t>
+          <t>-2,69; 596,3</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-71,8; 213,2</t>
+          <t>-68,56; 239,6</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-31,25; 737,62</t>
+          <t>97,9; 1383,0</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3,11</t>
+          <t>3,3</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,24</t>
+          <t>0,93</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1,98</t>
+          <t>2,35</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,81; 3,42</t>
+          <t>0,62; 3,32</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 1,48</t>
+          <t>-0,3; 1,47</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,43; 5,52</t>
+          <t>1,33; 5,57</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,32; -0,0</t>
+          <t>-1,41; -0,07</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 1,29</t>
+          <t>-0,57; 1,27</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 1,55</t>
+          <t>-0,29; 3,5</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 1,29</t>
+          <t>-0,09; 1,27</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 1,14</t>
+          <t>-0,18; 1,09</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,85; 3,56</t>
+          <t>1,1; 4,02</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>398,32%</t>
+          <t>423,28%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>116,57%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>250,7%</t>
+          <t>298,76%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>47,69; 812,08</t>
+          <t>27,51; 806,85</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-40,25; 402,59</t>
+          <t>-35,32; 376,22</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>78,01; 1247,84</t>
+          <t>77,55; 1296,01</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 115,35</t>
+          <t>-100,0; 111,84</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-51,99; 353,45</t>
+          <t>-52,83; 337,81</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-69,02; 332,63</t>
+          <t>-53,42; 730,9</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-6,4; 254,95</t>
+          <t>-10,85; 261,4</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-20,4; 243,47</t>
+          <t>-22,34; 212,91</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>72,42; 638,44</t>
+          <t>82,93; 670,78</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1,46</t>
+          <t>1,68</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,04</t>
+          <t>1,58</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1,35</t>
+          <t>1,73</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,63; 1,79</t>
+          <t>0,56; 1,73</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,24</t>
+          <t>0,18; 1,2</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,45</t>
+          <t>0,9; 2,54</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 0,07</t>
+          <t>-0,42; 0,09</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 0,49</t>
+          <t>-0,09; 0,54</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,03</t>
+          <t>0,79; 2,85</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,78</t>
+          <t>0,2; 0,8</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,72</t>
+          <t>0,11; 0,71</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,64; 1,93</t>
+          <t>1,16; 2,39</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>186,74%</t>
+          <t>214,75%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>377,6%</t>
+          <t>575,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>257,9%</t>
+          <t>329,07%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>58,31; 310,93</t>
+          <t>55,08; 312,55</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>10,24; 200,54</t>
+          <t>16,13; 212,68</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>75,12; 409,43</t>
+          <t>84,5; 436,34</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-88,11; 85,72</t>
+          <t>-88,23; 99,41</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-37,4; 312,52</t>
+          <t>-30,8; 367,24</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>50,07; 1035,17</t>
+          <t>143,35; 1685,86</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>25,21; 201,8</t>
+          <t>27,97; 197,99</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>17,59; 189,01</t>
+          <t>16,44; 184,63</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>110,68; 455,96</t>
+          <t>167,37; 560,9</t>
         </is>
       </c>
     </row>
